--- a/results/summary_stats.xlsx
+++ b/results/summary_stats.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,52 +417,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>portfolio</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>start_date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>end_date</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>n_months</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ann_mean_return</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ann_volatility</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>sharpe_ratio</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>min_monthly_return</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>max_monthly_return</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ann_cumulative_return</t>
         </is>
@@ -538,22 +526,22 @@
         <v>144</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06651032845916201</v>
+        <v>0.0665103284591663</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1178028585475991</v>
+        <v>0.1178028585476008</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5645901065489684</v>
+        <v>0.5645901065489961</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1247491258960358</v>
+        <v>-0.124749125896036</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1110485181262049</v>
+        <v>0.111048518126205</v>
       </c>
       <c r="J3" t="n">
-        <v>1.040423568103589</v>
+        <v>1.040423568103686</v>
       </c>
     </row>
   </sheetData>

--- a/results/summary_stats.xlsx
+++ b/results/summary_stats.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,52 +429,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>portfolio</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>start_date</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>end_date</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>n_months</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ann_mean_return</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>ann_volatility</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>sharpe_ratio</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>min_monthly_return</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>max_monthly_return</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ann_cumulative_return</t>
         </is>
@@ -488,22 +500,22 @@
         <v>144</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1160431582921533</v>
+        <v>0.115415265020771</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1416289221943703</v>
+        <v>0.1419466149612895</v>
       </c>
       <c r="G2" t="n">
-        <v>0.81934647594717</v>
+        <v>0.6899795746977162</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1306646275006716</v>
+        <v>-0.1313266858354276</v>
       </c>
       <c r="I2" t="n">
-        <v>0.128390056224827</v>
+        <v>0.1287856698772998</v>
       </c>
       <c r="J2" t="n">
-        <v>2.550527491677803</v>
+        <v>2.522228222836635</v>
       </c>
     </row>
     <row r="3">
@@ -526,22 +538,22 @@
         <v>144</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0665103284591663</v>
+        <v>0.06376284546272912</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1178028585476008</v>
+        <v>0.1196165469892006</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5645901065489961</v>
+        <v>0.3869685810852587</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.124749125896036</v>
+        <v>-0.1455370694095079</v>
       </c>
       <c r="I3" t="n">
-        <v>0.111048518126205</v>
+        <v>0.1199592192394579</v>
       </c>
       <c r="J3" t="n">
-        <v>1.040423568103686</v>
+        <v>0.9687677805291184</v>
       </c>
     </row>
   </sheetData>

--- a/results/summary_stats.xlsx
+++ b/results/summary_stats.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,6 +476,11 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>cumulative_return</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>ann_cumulative_return</t>
         </is>
       </c>
@@ -517,6 +522,9 @@
       <c r="J2" t="n">
         <v>2.522228222836635</v>
       </c>
+      <c r="K2" t="n">
+        <v>0.1106267370252159</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -554,6 +562,9 @@
       </c>
       <c r="J3" t="n">
         <v>0.9687677805291184</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.05807440238367145</v>
       </c>
     </row>
   </sheetData>

--- a/results/summary_stats.xlsx
+++ b/results/summary_stats.xlsx
@@ -505,25 +505,25 @@
         <v>144</v>
       </c>
       <c r="E2" t="n">
-        <v>0.115415265020771</v>
+        <v>0.1161089684026302</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1419466149612895</v>
+        <v>0.1417472954542222</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6899795746977162</v>
+        <v>0.6958437414030544</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1313266858354276</v>
+        <v>-0.1306650921429244</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1287856698772998</v>
+        <v>0.1283940181539289</v>
       </c>
       <c r="J2" t="n">
-        <v>2.522228222836635</v>
+        <v>2.552606133086479</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1106267370252159</v>
+        <v>0.1114218275345946</v>
       </c>
     </row>
     <row r="3">
@@ -546,25 +546,25 @@
         <v>144</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06376284546272912</v>
+        <v>0.06651032845916199</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1196165469892006</v>
+        <v>0.117802858547599</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3869685810852587</v>
+        <v>0.4162490542565989</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1455370694095079</v>
+        <v>-0.1247491258960358</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1199592192394579</v>
+        <v>0.1110485181262049</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9687677805291184</v>
+        <v>1.040423568103589</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05807440238367145</v>
+        <v>0.06123124381065237</v>
       </c>
     </row>
   </sheetData>

--- a/results/summary_stats.xlsx
+++ b/results/summary_stats.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,57 +417,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>portfolio</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>start_date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>end_date</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>n_months</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ann_mean_return</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ann_volatility</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>sharpe_ratio</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>min_monthly_return</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>max_monthly_return</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>cumulative_return</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ann_cumulative_return</t>
         </is>
@@ -546,25 +534,25 @@
         <v>144</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06651032845916199</v>
+        <v>0.06651032845916628</v>
       </c>
       <c r="F3" t="n">
-        <v>0.117802858547599</v>
+        <v>0.1178028585476008</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4162490542565989</v>
+        <v>0.4162490542566288</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1247491258960358</v>
+        <v>-0.124749125896036</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1110485181262049</v>
+        <v>0.111048518126205</v>
       </c>
       <c r="J3" t="n">
-        <v>1.040423568103589</v>
+        <v>1.040423568103686</v>
       </c>
       <c r="K3" t="n">
-        <v>0.06123124381065237</v>
+        <v>0.06123124381065659</v>
       </c>
     </row>
   </sheetData>

--- a/results/summary_stats.xlsx
+++ b/results/summary_stats.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,57 +429,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>portfolio</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>start_date</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>end_date</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>n_months</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ann_mean_return</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>ann_volatility</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>sharpe_ratio</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>min_monthly_return</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>max_monthly_return</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>cumulative_return</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ann_cumulative_return</t>
         </is>
@@ -534,25 +546,25 @@
         <v>144</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06651032845916628</v>
+        <v>0.06651032845916199</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1178028585476008</v>
+        <v>0.117802858547599</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4162490542566288</v>
+        <v>0.4162490542565989</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.124749125896036</v>
+        <v>-0.1247491258960358</v>
       </c>
       <c r="I3" t="n">
-        <v>0.111048518126205</v>
+        <v>0.1110485181262049</v>
       </c>
       <c r="J3" t="n">
-        <v>1.040423568103686</v>
+        <v>1.040423568103589</v>
       </c>
       <c r="K3" t="n">
-        <v>0.06123124381065659</v>
+        <v>0.06123124381065237</v>
       </c>
     </row>
   </sheetData>

--- a/results/summary_stats.xlsx
+++ b/results/summary_stats.xlsx
@@ -534,25 +534,25 @@
         <v>144</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06651032845916628</v>
+        <v>0.06643431976102138</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1178028585476008</v>
+        <v>0.1184615823209638</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4162490542566288</v>
+        <v>0.4132928060032944</v>
       </c>
       <c r="H3" t="n">
         <v>-0.124749125896036</v>
       </c>
       <c r="I3" t="n">
-        <v>0.111048518126205</v>
+        <v>0.1110485181262049</v>
       </c>
       <c r="J3" t="n">
-        <v>1.040423568103686</v>
+        <v>1.036662757841087</v>
       </c>
       <c r="K3" t="n">
-        <v>0.06123124381065659</v>
+        <v>0.06106810509709115</v>
       </c>
     </row>
   </sheetData>

--- a/results/summary_stats.xlsx
+++ b/results/summary_stats.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,57 +429,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>portfolio</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>start_date</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>end_date</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>n_months</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ann_mean_return</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>ann_volatility</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>sharpe_ratio</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>min_monthly_return</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>max_monthly_return</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>cumulative_return</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ann_cumulative_return</t>
         </is>
@@ -534,25 +546,25 @@
         <v>144</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06643431976102138</v>
+        <v>0.0735968597172429</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1184615823209638</v>
+        <v>0.1158268157243262</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4132928060032944</v>
+        <v>0.4845325269997564</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.124749125896036</v>
+        <v>-0.1177459164809954</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1110485181262049</v>
+        <v>0.107370588150448</v>
       </c>
       <c r="J3" t="n">
-        <v>1.036662757841087</v>
+        <v>1.226928545643094</v>
       </c>
       <c r="K3" t="n">
-        <v>0.06106810509709115</v>
+        <v>0.06899462987138794</v>
       </c>
     </row>
   </sheetData>

--- a/results/summary_stats.xlsx
+++ b/results/summary_stats.xlsx
@@ -546,25 +546,25 @@
         <v>144</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0735968597172429</v>
+        <v>0.08699389136104067</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1158268157243262</v>
+        <v>0.1245634509958454</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4845325269997564</v>
+        <v>0.5581002357052497</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1177459164809954</v>
+        <v>-0.10868744661239</v>
       </c>
       <c r="I3" t="n">
-        <v>0.107370588150448</v>
+        <v>0.111363065630386</v>
       </c>
       <c r="J3" t="n">
-        <v>1.226928545643094</v>
+        <v>1.58204655507117</v>
       </c>
       <c r="K3" t="n">
-        <v>0.06899462987138794</v>
+        <v>0.08225683937321926</v>
       </c>
     </row>
   </sheetData>

--- a/results/summary_stats.xlsx
+++ b/results/summary_stats.xlsx
@@ -505,25 +505,25 @@
         <v>144</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1161089684026302</v>
+        <v>0.1154152650207711</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1417472954542222</v>
+        <v>0.1419466149612896</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6958437414030544</v>
+        <v>0.6899795746977162</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1306650921429244</v>
+        <v>-0.1313266858354276</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1283940181539289</v>
+        <v>0.1287856698772999</v>
       </c>
       <c r="J2" t="n">
-        <v>2.552606133086479</v>
+        <v>2.522228222836637</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1114218275345946</v>
+        <v>0.1106267370252159</v>
       </c>
     </row>
     <row r="3">
@@ -546,25 +546,25 @@
         <v>144</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08699389136104067</v>
+        <v>0.0735329503620184</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1245634509958454</v>
+        <v>0.1158376793180041</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5581002357052497</v>
+        <v>0.4839353713926274</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.10868744661239</v>
+        <v>-0.1177459164809955</v>
       </c>
       <c r="I3" t="n">
-        <v>0.111363065630386</v>
+        <v>0.107370588150448</v>
       </c>
       <c r="J3" t="n">
-        <v>1.58204655507117</v>
+        <v>1.225201158795513</v>
       </c>
       <c r="K3" t="n">
-        <v>0.08225683937321926</v>
+        <v>0.06892550536334396</v>
       </c>
     </row>
   </sheetData>

--- a/results/summary_stats.xlsx
+++ b/results/summary_stats.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,57 +417,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>portfolio</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>start_date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>end_date</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>n_months</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ann_mean_return</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ann_volatility</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>sharpe_ratio</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>min_monthly_return</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>max_monthly_return</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>cumulative_return</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ann_cumulative_return</t>
         </is>
@@ -546,13 +534,13 @@
         <v>144</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0735329503620184</v>
+        <v>0.07353295036201841</v>
       </c>
       <c r="F3" t="n">
         <v>0.1158376793180041</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4839353713926274</v>
+        <v>0.4839353713926273</v>
       </c>
       <c r="H3" t="n">
         <v>-0.1177459164809955</v>
